--- a/SAP/ROLES.xlsx
+++ b/SAP/ROLES.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="32">
   <si>
     <t xml:space="preserve">Профиль</t>
   </si>
